--- a/plantillas/Inicio-Cierre_Validacion.xlsx
+++ b/plantillas/Inicio-Cierre_Validacion.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Visual Studio Code\NodeJS\SIVACC\plantillas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3E7F81B6-A86A-41A4-8425-39DC564B649B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A76BD4C8-3A31-4366-99B5-16A2628AEEDB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ASISTENCIA INICIO Y CIERRE" sheetId="1" r:id="rId1"/>
@@ -222,7 +222,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -274,11 +274,17 @@
     <xf numFmtId="0" fontId="4" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -619,8 +625,8 @@
       <c r="T2" s="3"/>
       <c r="U2" s="3"/>
     </row>
-    <row r="3" spans="1:21" ht="20.25" x14ac:dyDescent="0.25">
-      <c r="A3" s="6"/>
+    <row r="3" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="20"/>
       <c r="B3" s="6"/>
       <c r="C3" s="3"/>
       <c r="D3" s="3"/>
@@ -642,7 +648,8 @@
       <c r="T3" s="3"/>
       <c r="U3" s="3"/>
     </row>
-    <row r="4" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="21"/>
       <c r="B4" s="1"/>
     </row>
     <row r="5" spans="1:21" ht="18" x14ac:dyDescent="0.25">
@@ -697,14 +704,16 @@
       <c r="U7" s="2"/>
     </row>
     <row r="8" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A8" s="22"/>
+      <c r="B8" s="22"/>
       <c r="K8" s="12"/>
       <c r="T8" s="9"/>
-      <c r="U8" s="2"/>
+      <c r="U8" s="9"/>
     </row>
     <row r="9" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="K9" s="12"/>
       <c r="T9" s="9"/>
-      <c r="U9" s="2"/>
+      <c r="U9" s="9"/>
     </row>
     <row r="10" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A10" s="13"/>
@@ -733,7 +742,7 @@
       <c r="A11" s="10" t="s">
         <v>0</v>
       </c>
-      <c r="B11" s="19"/>
+      <c r="B11" s="14"/>
       <c r="C11" s="15"/>
       <c r="D11" s="16"/>
       <c r="E11" s="16"/>
@@ -756,7 +765,7 @@
     </row>
     <row r="12" spans="1:21" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="18"/>
-      <c r="B12" s="20" t="s">
+      <c r="B12" s="19" t="s">
         <v>1</v>
       </c>
       <c r="C12" s="11" t="s">
@@ -842,5 +851,6 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>